--- a/mode_docx_gen/pmi_tokz/to_modes/ТО_3.xlsx
+++ b/mode_docx_gen/pmi_tokz/to_modes/ТО_3.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -466,10 +466,6 @@
     <col width="20" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="20" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="20" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,115 +521,95 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_hvptoc1_strpalc</t>
+          <t>SGF1_ptoc1_ltcblktoc</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Iset_hvptoc1_strpalc</t>
+          <t>Iset_ptoc1_ltcblktoc</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_lvptoc1_strpalc</t>
+          <t>SGF1_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Iset_lvptoc1_strpalc</t>
+          <t>SGF2_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_lvptoc2_strpalc</t>
+          <t>T1_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Iset_lvptoc2_strpalc</t>
+          <t>I2set_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_nsptoc1_lvnstoc</t>
+          <t>RatioSet_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_nsptoc1_lvnstoc</t>
+          <t>In_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>T1_nsptoc1_lvnstoc</t>
+          <t>SGF1_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>I2set_nsptoc1_lvnstoc</t>
+          <t>SGF2_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>RatioSet_nsptoc1_lvnstoc</t>
+          <t>SGF3_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>In_nsptoc1_lvnstoc</t>
+          <t>T1_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptrc1_ttoclgc</t>
+          <t>SGF1_ptrc1_tofflvlgc</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_ptrc1_ttoclgc</t>
+          <t>SGF1_rbre1_tofflvlgc</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_ptrc1_ttoclgc</t>
+          <t>SGF2_rbre1_tofflvlgc</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>T1_ptrc1_ttoclgc</t>
+          <t>SGF3_rbre1_tofflvlgc</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptrc1_tofflvlgc</t>
+          <t>SGF1_rblc1_tofflvlgc</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_rbre1_tofflvlgc</t>
+          <t>SGF2_rblc1_tofflvlgc</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_rbre1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>SGF3_rbre1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_rblc1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_rblc1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>SGF3_rblc1_tofflvlgc</t>
         </is>
@@ -679,64 +655,52 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>1</v>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
+      <c r="W2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="2" t="n">
-        <v>1</v>
+      <c r="Z2" t="n">
+        <v>0</v>
       </c>
       <c r="AA2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" s="2" t="n">
-        <v>1</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -751,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -779,15 +743,6 @@
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="20" customWidth="1" min="27" max="27"/>
-    <col width="20" customWidth="1" min="28" max="28"/>
-    <col width="20" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="20" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="20" customWidth="1" min="33" max="33"/>
-    <col width="20" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -828,135 +783,90 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>IA1</t>
+          <t>OV_ptoc1_lvtoc</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>IB1</t>
+          <t>NaSign_ptoc1_lvtoc</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>IC1</t>
+          <t>OV_hvptoc1_lovctoc</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>IA2</t>
+          <t>NaOtkl_hvptoc1_lovctoc</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>IB2</t>
+          <t>OV_ptoc1_lvarctoc</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>IC2</t>
+          <t>mtz1_pusk</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>OV_ptoc1_lvtoc</t>
+          <t>mtz2_pusk</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>NaSign_ptoc1_lvtoc</t>
+          <t>mtz3_pusk</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>OV_hvptoc1_lovctoc</t>
+          <t>OV_ptoc1_ltcblktoc</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NaOtkl_hvptoc1_lovctoc</t>
+          <t>OV_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>OV_ptoc1_lvarctoc</t>
+          <t>NaSign_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mtz1_pusk</t>
+          <t>OV_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>mtz2_pusk</t>
+          <t>vnesh_pusk_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>mtz3_pusk</t>
+          <t>blok_lzt_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>OV_strpalc</t>
+          <t>OV_tofflvlg</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>OV_hvptoc1_strpalc</t>
+          <t>OVlo_tofflvlg</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>OV_lvptoc1_strpalc</t>
+          <t>OVzapv_tofflvlg</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lvptoc2_strpalc</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>OV_nsptoc1_lvnstoc</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>NaSign_nsptoc1_lvnstoc</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptrc1_ttoclgc</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_pusk_ptrc1_ttoclgc</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>blok_lzt_ptrc1_ttoclgc</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>OV_tofflvlg</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>OVlo_tofflvlg</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>OVzapv_tofflvlg</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>OVzavr_tofflvlg</t>
         </is>
@@ -1036,33 +946,6 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1077,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF2"/>
+  <dimension ref="A1:AV2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1128,16 +1011,6 @@
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="20" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
-    <col width="20" customWidth="1" min="50" max="50"/>
-    <col width="20" customWidth="1" min="51" max="51"/>
-    <col width="20" customWidth="1" min="52" max="52"/>
-    <col width="20" customWidth="1" min="53" max="53"/>
-    <col width="20" customWidth="1" min="54" max="54"/>
-    <col width="20" customWidth="1" min="55" max="55"/>
-    <col width="20" customWidth="1" min="56" max="56"/>
-    <col width="20" customWidth="1" min="57" max="57"/>
-    <col width="20" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,210 +1096,160 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>vvod_hvptoc1_strpalc</t>
+          <t>vvod_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_hvptoc1_strpalc</t>
+          <t>oper_vyvod_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>pusk_hvptoc1_strpalc</t>
+          <t>srab_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>io_hvptoc1_strpalc</t>
+          <t>srabsign_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>vvod_lvptoc1_strpalc</t>
+          <t>pusk_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_lvptoc1_strpalc</t>
+          <t>io_I2_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>pusk_lvptoc1_strpalc</t>
+          <t>io_rat_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>io_lvptoc1_strpalc</t>
+          <t>vvod_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>vvod_lvptoc2_strpalc</t>
+          <t>oper_vyvod_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_lvptoc2_strpalc</t>
+          <t>pusk_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>pusk_lvptoc2_strpalc</t>
+          <t>srab_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>io_lvptoc2_strpalc</t>
+          <t>vvod_ptrc1_tofflvlgc</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>pusk_strpalc</t>
+          <t>oper_vyvod_ptrc1_tofflvlgc</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>vvod_strpalc</t>
+          <t>pusk_ptrc1_tofflvlgc</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>vvod_nsptoc1_lvnstoc</t>
+          <t>srab_ptrc1_tofflvlgc</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_nsptoc1_lvnstoc</t>
+          <t>vvod_rblc1_tofflvlgc</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>srab_nsptoc1_lvnstoc</t>
+          <t>oper_vyvod_rblc1_tofflvlgc</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>srabsign_nsptoc1_lvnstoc</t>
+          <t>zapret_rblc1_tofflvlgc</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>pusk_nsptoc1_lvnstoc</t>
+          <t>vvod_rbre1_tofflvlgc</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>io_I2_nsptoc1_lvnstoc</t>
+          <t>oper_vyvod_rbre1_tofflvlgc</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>io_rat_nsptoc1_lvnstoc</t>
+          <t>zapret_rbre1_tofflvlgc</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>vvod_ptrc1_ttoclgc</t>
+          <t>pusk_lvalv</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_ptrc1_ttoclgc</t>
+          <t>vvod_ptoc1_ltcblktoc</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>pusk_ptrc1_ttoclgc</t>
+          <t>oper_vyvod_ptoc1_ltcblktoc</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>srab_ptrc1_ttoclgc</t>
+          <t>pusk_ptoc1_ltcblktoc</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>vvod_ptrc1_tofflvlgc</t>
+          <t>io_ptoc1_ltcblktoc</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_ptrc1_tofflvlgc</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>pusk_ptrc1_tofflvlgc</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>srab_ptrc1_tofflvlgc</t>
+          <t>ICA</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>vvod_rblc1_tofflvlgc</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_rblc1_tofflvlgc</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>zapret_rblc1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_rbre1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_rbre1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>zapret_rbre1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_lvalv</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>IAB</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>I0</t>
         </is>
@@ -1568,9 +1391,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1578,19 +1401,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1603,9 +1426,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1613,14 +1436,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1638,87 +1461,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AS2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AY2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BA2" s="2" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="BB2" s="2" t="inlineStr">
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
+      <c r="AV2" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>

--- a/mode_docx_gen/pmi_tokz/to_modes/ТО_3.xlsx
+++ b/mode_docx_gen/pmi_tokz/to_modes/ТО_3.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SGF_Parameters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -455,17 +456,6 @@
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="20" customWidth="1" min="27" max="27"/>
-    <col width="20" customWidth="1" min="28" max="28"/>
-    <col width="20" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,135 +471,80 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>T1_ptoc1_lvtoc</t>
+          <t>SGF1_hvptoc1_lovctoc</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Iset_ptoc1_lvtoc</t>
+          <t>SGF1_ptoc1_lvarctoc</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_hvptoc1_lovctoc</t>
+          <t>SGF2_ptoc1_lvarctoc</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1_hvptoc1_lovctoc</t>
+          <t>SGF1_ptoc1_ltcblktoc</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Iset_hvptoc1_lovctoc</t>
+          <t>SGF1_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptoc1_lvarctoc</t>
+          <t>SGF2_nsptoc1_lvnstoc</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_ptoc1_lvarctoc</t>
+          <t>SGF1_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Iset_ptoc1_lvarctoc</t>
+          <t>SGF2_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptoc1_ltcblktoc</t>
+          <t>SGF3_ptrc1_ttoclgc</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Iset_ptoc1_ltcblktoc</t>
+          <t>SGF1_ptrc1_tofflvlgc</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_nsptoc1_lvnstoc</t>
+          <t>SGF1_rbre1_tofflvlgc</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_nsptoc1_lvnstoc</t>
+          <t>SGF2_rbre1_tofflvlgc</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>T1_nsptoc1_lvnstoc</t>
+          <t>SGF3_rbre1_tofflvlgc</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>I2set_nsptoc1_lvnstoc</t>
+          <t>SGF1_rblc1_tofflvlgc</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>RatioSet_nsptoc1_lvnstoc</t>
+          <t>SGF2_rblc1_tofflvlgc</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>In_nsptoc1_lvnstoc</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_ptrc1_ttoclgc</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_ptrc1_ttoclgc</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>SGF3_ptrc1_ttoclgc</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>T1_ptrc1_ttoclgc</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_ptrc1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_rbre1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_rbre1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>SGF3_rbre1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_rblc1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_rblc1_tofflvlgc</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>SGF3_rblc1_tofflvlgc</t>
         </is>
@@ -622,20 +557,20 @@
       <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>1</v>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -643,8 +578,8 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
+      <c r="J2" t="n">
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -652,55 +587,22 @@
       <c r="L2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>1</v>
+      <c r="O2" t="n">
+        <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -710,6 +612,125 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>T1_ptoc1_lvtoc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Iset_ptoc1_lvtoc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>T1_hvptoc1_lovctoc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Iset_hvptoc1_lovctoc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Iset_ptoc1_lvarctoc</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Iset_ptoc1_ltcblktoc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>T1_nsptoc1_lvnstoc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>I2set_nsptoc1_lvnstoc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>RatioSet_nsptoc1_lvnstoc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>In_nsptoc1_lvnstoc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>T1_ptrc1_ttoclgc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -954,7 +975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/mode_docx_gen/pmi_tokz/to_modes/ТО_3.xlsx
+++ b/mode_docx_gen/pmi_tokz/to_modes/ТО_3.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -456,6 +456,7 @@
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,6 +550,11 @@
           <t>SGF3_rblc1_tofflvlgc</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Номинальный ток входа</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -604,6 +610,9 @@
       </c>
       <c r="R2" t="n">
         <v>0</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -617,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -630,7 +639,6 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -681,11 +689,6 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>In_nsptoc1_lvnstoc</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
           <t>T1_ptrc1_ttoclgc</t>
         </is>
       </c>
@@ -695,33 +698,30 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
